--- a/Result/checksun_type/藍寶石晶圓_晶片.xlsx
+++ b/Result/checksun_type/藍寶石晶圓_晶片.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>105</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>103180579</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>78066930</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>136094275</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>116900919</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>146495369</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>194852695</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>218463765</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>434797068</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>208362204</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>128273399</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>276385084</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>23.32</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>23312.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>9629.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>9629.200000000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>14884.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>7449.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>7449.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>816.5911899499497</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>23312</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>23312.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>23.09</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4013.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>6324.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>6324</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>13005.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>7283.74</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>7283.74</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-343.1385080735217</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4013</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4013.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>23.13</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23.28</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>5494.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7527.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7527.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>12868.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>7378.32</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>7378.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>80.10972718128687</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>5494</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>5494.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>7065.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>8284.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>8284.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>12587.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>7563.22</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>7563.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>523.2104301459694</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>7065</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>7065.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>23.49</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>8262.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>14123.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>14123</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>12216.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>7629.54</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>7629.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>969.2039190188734</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>8262</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>23.55</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23.42</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6786.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>20139.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>11594.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>7648.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1443.473048872349</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6786</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6786.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>23.31</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>10030.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>19686.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>19686.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>11202.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>8102.12</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>8102.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2227.590625489014</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>10030</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>10030.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>22.87</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23.5</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>9279.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>18210.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>18210.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>10729.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>8369.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>8369.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2920.630355459645</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>9279</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>9279.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>22.35</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>23.54</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>36258.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>16891.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>16891</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>10195.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>10437.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>10437.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>3886.843171294131</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>36258</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>36258.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>22.29</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>38343.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>10310.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>10310.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>7058.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>13160.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>13160.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2237.724223511461</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>38343</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>21.53</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>22.23</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>23.66</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4524.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3050.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3050</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3638.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>12810.66</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>12810.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-421.4715670177616</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4524</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4524.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>13.56</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>14268504.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7249024.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7249024</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4013502.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1806762.58</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1806762.58</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1860277.105062644</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>14268504</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>14268504.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13.48</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>19324917.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4474500.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4474500.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2680782.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1559186.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1559186.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>1298075.861681122</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>19324917</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>19324917.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13.42</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.12</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>747352.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>738435.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>738435.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>889759.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1194825.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1194825</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-93187.15963823383</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>747352</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>747352.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>13.73</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>13.13</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>890136.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>963018.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>963018</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1200071.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1209385.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1209385.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-86924.25582166249</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>890136</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>890136.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>13.72</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.14</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1014211.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>826858.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>826858.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1204934.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1209173.9</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1209173.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-90171.0983757868</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1014211</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1014211.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>13.36</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>13.15</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>395887.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>777981.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>777981</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1295516.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1214275.24</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1214275.24</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-104882.7985111149</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>395887</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>395887.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>13.84</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>13.16</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>644591.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>887064.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>887064.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1310132.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1256904.46</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1256904.46</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-55904.69875761541</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>644591</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>644591.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.18</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1870265.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1041083.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1041083.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1295875.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1300658.24</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1300658.24</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-10586.24558270094</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1870265</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1870265.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>13.74</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>209340.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1437124.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1437124.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1160130.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1291148.76</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1291148.76</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-76789.73227629834</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>209340</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>209340.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>13.68</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>13.17</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.17</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>769822.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1583011.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1583011</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1216033.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1347530.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1347530</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>9332.598599859048</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>769822</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>769822.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>13.56</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13.19</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.19</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>941304.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1813051.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1813051</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1258842.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1473262.06</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1473262.06</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>71979.5499015178</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>941304</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>941304.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>403535423</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>363440217</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>451484020</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>569640781</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1056628890</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>436450840</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>365688993</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>676579414</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>622810797</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>566992376</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>832928036</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
